--- a/data/valuation/jordan_valuation.xlsx
+++ b/data/valuation/jordan_valuation.xlsx
@@ -11,7 +11,8 @@
     <sheet name="Inputs" sheetId="2" r:id="rId2"/>
     <sheet name="Model" sheetId="3" r:id="rId3"/>
     <sheet name="Valuation" sheetId="4" r:id="rId4"/>
-    <sheet name="Checks" sheetId="5" r:id="rId5"/>
+    <sheet name="Charts" sheetId="5" r:id="rId5"/>
+    <sheet name="Checks" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="k_Inputs_case">Inputs!$A$5</definedName>
@@ -55,14 +56,232 @@
     <definedName name="k_Valuation_tv">Valuation!$A$6</definedName>
     <definedName name="k_Valuation_tv_share">Valuation!$A$13</definedName>
     <definedName name="k_Valuation_vs_peak">Valuation!$A$17</definedName>
-    <definedName name="MasterCheck">Checks!$D$7</definedName>
+    <definedName name="MasterCheck">Checks!$D$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">Inputs!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">Model!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">Valuation!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: FY2026 Form 10-K (filed 2026-07-15) p. 32</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: FY2026 Form 10-K (filed 2026-07-15) p. 32</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: market data, data/valuation/peer_multiples.csv (Oct 13, 2026)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: Convention shared with the reverse DCF (research_notes/thesis_tests/consensus_and_valuation.md Section C)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: Convention shared with the reverse DCF (research_notes/thesis_tests/consensus_and_valuation.md Section C)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: Convention shared with the reverse DCF (research_notes/thesis_tests/consensus_and_valuation.md Section C)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: Convention shared with the reverse DCF (research_notes/thesis_tests/consensus_and_valuation.md Section C)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: Convention shared with the reverse DCF (research_notes/thesis_tests/consensus_and_valuation.md Section C)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: FY2027 consolidated margin implied by consensus EPS; Convention shared with the reverse DCF (research_notes/thesis_tests/consensus_and_valuation.md Section C)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: Convention shared with the reverse DCF (research_notes/thesis_tests/consensus_and_valuation.md Section C)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: ASSUMPTION; see research_notes/12_jordan_brand_thesis.md</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D22" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: ASSUMPTION</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: ASSUMPTION; FY2027 -15% from Q1 FY27 'mid-teens' decline (Nike transcript, Oct 1, 2026)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: ASSUMPTION; FY2027 -15% from Q1 FY27 'mid-teens' decline (Nike transcript, Oct 1, 2026)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: ASSUMPTION; FY2027 -15% from Q1 FY27 'mid-teens' decline (Nike transcript, Oct 1, 2026)</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="142">
   <si>
     <t>Inputs</t>
   </si>
@@ -313,6 +532,99 @@
     <t>FY2031 revenue vs FY2024 peak</t>
   </si>
   <si>
+    <t>Charts</t>
+  </si>
+  <si>
+    <t>Jordan DCF value, active scenario ($m)</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>Running total</t>
+  </si>
+  <si>
+    <t>Increase</t>
+  </si>
+  <si>
+    <t>Decrease</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>PV FY2027 FCF</t>
+  </si>
+  <si>
+    <t>PV FY2028 FCF</t>
+  </si>
+  <si>
+    <t>PV FY2029 FCF</t>
+  </si>
+  <si>
+    <t>PV FY2030 FCF</t>
+  </si>
+  <si>
+    <t>PV FY2031 FCF</t>
+  </si>
+  <si>
+    <t>PV terminal value</t>
+  </si>
+  <si>
+    <t>End</t>
+  </si>
+  <si>
+    <t>Live: follows the scenario switch on Inputs. End bar equals Valuation 'DCF value of Jordan'.</t>
+  </si>
+  <si>
+    <t>Jordan value per NKE share ($)</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>DCF, Bear to Bull scenarios</t>
+  </si>
+  <si>
+    <t>data/valuation/jordan_scenarios.csv (scripts/jordan_valuation.py)</t>
+  </si>
+  <si>
+    <t>DCF, Base path, margin 6% to 17%</t>
+  </si>
+  <si>
+    <t>data/valuation/jordan_sensitivity.csv</t>
+  </si>
+  <si>
+    <t>DCF, Bear path, margin 6% to 17%</t>
+  </si>
+  <si>
+    <t>Jordan FY2026 revenue x NKE EV/Sales</t>
+  </si>
+  <si>
+    <t>jordan_scenarios.csv reference row (point estimate)</t>
+  </si>
+  <si>
+    <t>Live scenario value per share</t>
+  </si>
+  <si>
+    <t>live marker (column F), drawn as a sliver of width set in column G</t>
+  </si>
+  <si>
+    <t>Static ranges are outputs of scripts/jordan_valuation.py; the marker is live.</t>
+  </si>
+  <si>
     <t>Check</t>
   </si>
   <si>
@@ -325,18 +637,24 @@
     <t>Margin reaches target in FY2031</t>
   </si>
   <si>
-    <t>WACC above terminal growth</t>
+    <t>Terminal growth below WACC</t>
   </si>
   <si>
     <t>must be 1</t>
   </si>
   <si>
+    <t>Revenue never negative</t>
+  </si>
+  <si>
     <t>Value = PV(FCF) + PV(TV)</t>
   </si>
   <si>
     <t>Discount timing ends at 4.63 years</t>
   </si>
   <si>
+    <t>Jordan DCF value, active scenario ($m): bars reconcile</t>
+  </si>
+  <si>
     <t>Master check (1 = all pass)</t>
   </si>
   <si>
@@ -386,23 +704,27 @@
   </si>
   <si>
     <t>DCF value, per-share value and terminal share for the active scenario</t>
+  </si>
+  <si>
+    <t>Value bridge for the active scenario and the per-share football field</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="@"/>
     <numFmt numFmtId="165" formatCode="#,##0_);(#,##0);&quot;-&quot;_)"/>
     <numFmt numFmtId="166" formatCode="$#,##0.00_);($#,##0.00);&quot;-&quot;_)"/>
     <numFmt numFmtId="167" formatCode="0.0%_);(0.0%);&quot;-&quot;_)"/>
     <numFmt numFmtId="168" formatCode="0.0&quot;x&quot;"/>
     <numFmt numFmtId="169" formatCode="0.00"/>
-    <numFmt numFmtId="170" formatCode="#,##0.000000"/>
-    <numFmt numFmtId="171" formatCode="0.000000"/>
+    <numFmt numFmtId="170" formatCode="0.0%"/>
+    <numFmt numFmtId="171" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="172" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -449,6 +771,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -491,7 +819,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -517,8 +845,10 @@
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
@@ -528,6 +858,645 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" baseline="0">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" baseline="0">
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Jordan DCF value, active scenario ($m)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Base</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Charts!$A$5:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>PV FY2027 FCF</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>PV FY2028 FCF</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>PV FY2029 FCF</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>PV FY2030 FCF</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>PV FY2031 FCF</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>PV terminal value</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>End</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Charts!$D$5:$D$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Total</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="1F4E79"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Charts!$A$5:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>PV FY2027 FCF</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>PV FY2028 FCF</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>PV FY2029 FCF</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>PV FY2030 FCF</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>PV FY2031 FCF</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>PV terminal value</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>End</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Charts!$G$5:$G$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Increase</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="548235"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Charts!$A$5:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>PV FY2027 FCF</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>PV FY2028 FCF</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>PV FY2029 FCF</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>PV FY2030 FCF</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>PV FY2031 FCF</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>PV terminal value</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>End</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Charts!$E$5:$E$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>Decrease</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="C00000"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Charts!$A$5:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>PV FY2027 FCF</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>PV FY2028 FCF</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>PV FY2029 FCF</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>PV FY2030 FCF</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>PV FY2031 FCF</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>PV terminal value</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>End</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Charts!$F$5:$F$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="50"/>
+        <c:overlap val="100"/>
+        <c:axId val="50010001"/>
+        <c:axId val="50010002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50010001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50010002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50010002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0_);(#,##0);&quot;-&quot;_)" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50010001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" baseline="0">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" baseline="0">
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Jordan value per NKE share ($)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Low</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Charts!$A$38:$A$42</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>DCF, Bear to Bull scenarios</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>DCF, Base path, margin 6% to 17%</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>DCF, Bear path, margin 6% to 17%</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Jordan FY2026 revenue x NKE EV/Sales</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Live scenario value per share</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Charts!$B$38:$B$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2.32</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.14</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.82</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.68</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Range</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="1F4E79"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Charts!$A$38:$A$42</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>DCF, Bear to Bull scenarios</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>DCF, Base path, margin 6% to 17%</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>DCF, Bear path, margin 6% to 17%</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Jordan FY2026 revenue x NKE EV/Sales</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Live scenario value per share</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Charts!$D$38:$D$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="60"/>
+        <c:overlap val="100"/>
+        <c:axId val="50020001"/>
+        <c:axId val="50020002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50020001"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50020002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50020002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="t"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="$#,##0.00_);($#,##0.00);&quot;-&quot;_)" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50020001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -815,7 +1784,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -824,17 +1796,17 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="B4" s="1" t="str">
         <f>IF(MasterCheck=1,"OK: all checks pass","ERROR: see Checks sheet")</f>
@@ -843,44 +1815,44 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="5" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="6" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -888,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -896,7 +1868,7 @@
         <v>41</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -904,16 +1876,31 @@
         <v>68</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>107</v>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" fitToHeight="0" orientation="landscape"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;A&amp;R&amp;P of &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1197,11 +2184,19 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" fitToHeight="0" orientation="landscape"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;A&amp;R&amp;P of &amp;N</oddFooter>
+  </headerFooter>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1698,11 +2693,19 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" fitToHeight="0" orientation="landscape"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;A&amp;R&amp;P of &amp;N</oddFooter>
+  </headerFooter>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1880,12 +2883,372 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" fitToHeight="0" orientation="landscape"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;A&amp;R&amp;P of &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G44"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="38.7109375" customWidth="1"/>
+    <col min="2" max="7" width="12.7109375" customWidth="1"/>
+    <col min="8" max="8" width="60.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="24">
+        <f>Model!$C$22</f>
+        <v>161.47292095919</v>
+      </c>
+      <c r="C5" s="10">
+        <f>B5</f>
+        <v>161.47292095919</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10">
+        <f>B5</f>
+        <v>161.47292095919</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="24">
+        <f>Model!$D$22</f>
+        <v>283.509307261502</v>
+      </c>
+      <c r="C6" s="10">
+        <f>C5+B6</f>
+        <v>444.982228220691</v>
+      </c>
+      <c r="D6" s="10">
+        <f>MIN(C5,C6)</f>
+        <v>161.47292095919</v>
+      </c>
+      <c r="E6" s="10">
+        <f>MAX(B6,0)</f>
+        <v>283.509307261502</v>
+      </c>
+      <c r="F6" s="10">
+        <f>MAX(-B6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="24">
+        <f>Model!$E$22</f>
+        <v>226.985561882892</v>
+      </c>
+      <c r="C7" s="10">
+        <f>C6+B7</f>
+        <v>671.967790103583</v>
+      </c>
+      <c r="D7" s="10">
+        <f>MIN(C6,C7)</f>
+        <v>444.982228220691</v>
+      </c>
+      <c r="E7" s="10">
+        <f>MAX(B7,0)</f>
+        <v>226.985561882892</v>
+      </c>
+      <c r="F7" s="10">
+        <f>MAX(-B7,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" s="24">
+        <f>Model!$F$22</f>
+        <v>265.390596257345</v>
+      </c>
+      <c r="C8" s="10">
+        <f>C7+B8</f>
+        <v>937.358386360928</v>
+      </c>
+      <c r="D8" s="10">
+        <f>MIN(C7,C8)</f>
+        <v>671.967790103583</v>
+      </c>
+      <c r="E8" s="10">
+        <f>MAX(B8,0)</f>
+        <v>265.390596257345</v>
+      </c>
+      <c r="F8" s="10">
+        <f>MAX(-B8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" s="24">
+        <f>Model!$G$22</f>
+        <v>299.835285436841</v>
+      </c>
+      <c r="C9" s="10">
+        <f>C8+B9</f>
+        <v>1237.19367179777</v>
+      </c>
+      <c r="D9" s="10">
+        <f>MIN(C8,C9)</f>
+        <v>937.358386360928</v>
+      </c>
+      <c r="E9" s="10">
+        <f>MAX(B9,0)</f>
+        <v>299.835285436841</v>
+      </c>
+      <c r="F9" s="10">
+        <f>MAX(-B9,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="24">
+        <f>Valuation!$C$7</f>
+        <v>4402.28172192655</v>
+      </c>
+      <c r="C10" s="10">
+        <f>C9+B10</f>
+        <v>5639.47539372432</v>
+      </c>
+      <c r="D10" s="10">
+        <f>MIN(C9,C10)</f>
+        <v>1237.19367179777</v>
+      </c>
+      <c r="E10" s="10">
+        <f>MAX(B10,0)</f>
+        <v>4402.28172192655</v>
+      </c>
+      <c r="F10" s="10">
+        <f>MAX(-B10,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="10"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="10">
+        <f>C10</f>
+        <v>5639.47539372432</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="21">
+        <f>C11</f>
+        <v>5639.47539372432</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B38" s="12">
+        <v>2.32</v>
+      </c>
+      <c r="C38" s="12">
+        <v>5.96</v>
+      </c>
+      <c r="D38" s="23">
+        <f>C38-B38</f>
+        <v>3.64</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" s="12">
+        <v>2.14</v>
+      </c>
+      <c r="C39" s="12">
+        <v>5.78</v>
+      </c>
+      <c r="D39" s="23">
+        <f>C39-B39</f>
+        <v>3.64</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B40" s="12">
+        <v>1.82</v>
+      </c>
+      <c r="C40" s="12">
+        <v>4.57</v>
+      </c>
+      <c r="D40" s="23">
+        <f>C40-B40</f>
+        <v>2.75</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B41" s="12">
+        <v>5.68</v>
+      </c>
+      <c r="C41" s="12">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="D41" s="23">
+        <f>C41-B41</f>
+        <v>0.0199999999999996</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B42" s="23">
+        <f>F42-ABS(F42)*G42</f>
+        <v>3.77355616459697</v>
+      </c>
+      <c r="C42" s="23">
+        <f>F42+ABS(F42)*G42</f>
+        <v>3.81148135218086</v>
+      </c>
+      <c r="D42" s="23">
+        <f>C42-B42</f>
+        <v>0.0379251875838893</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F42" s="25">
+        <f>Valuation!$C$11</f>
+        <v>3.79251875838892</v>
+      </c>
+      <c r="G42" s="26">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" fitToHeight="0" orientation="landscape"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;A&amp;R&amp;P of &amp;N</oddFooter>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="34" max="16383" man="1"/>
+  </rowBreaks>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -1894,88 +3257,120 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B2" s="25">
+        <v>117</v>
+      </c>
+      <c r="B2" s="27">
         <f>Model!$G$16-Inputs!$C$21</f>
         <v>0</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="28">
         <v>0.001</v>
       </c>
-      <c r="D2" s="27">
+      <c r="D2" s="29">
         <f>IF(ABS(B2)&lt;=C2,1,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B3" s="27">
-        <f>IF(Inputs!$C$17&gt;Inputs!$C$22,1,0)</f>
+        <v>118</v>
+      </c>
+      <c r="B3" s="29">
+        <f>IF(Inputs!$C$22&lt;Inputs!$C$17,1,0)</f>
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" s="27">
+        <v>119</v>
+      </c>
+      <c r="D3" s="29">
         <f>B3</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B4" s="25">
+        <v>120</v>
+      </c>
+      <c r="B4" s="29">
+        <f>IF(MIN(Model!$C$14:$G$14)&gt;=0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" s="29">
+        <f>B4</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="27">
         <f>Valuation!$C$10-SUM(Model!$C$22:$G$22)-Valuation!$C$7</f>
         <v>0</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C5" s="28">
         <v>0.001</v>
       </c>
-      <c r="D4" s="27">
-        <f>IF(ABS(B4)&lt;=C4,1,0)</f>
+      <c r="D5" s="29">
+        <f>IF(ABS(B5)&lt;=C5,1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B5" s="25">
+    <row r="6" spans="1:4">
+      <c r="A6" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" s="27">
         <f>Model!$G$7-(Inputs!$C$19+4)</f>
         <v>0</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C6" s="28">
         <v>0.001</v>
       </c>
-      <c r="D5" s="27">
-        <f>IF(ABS(B5)&lt;=C5,1,0)</f>
+      <c r="D6" s="29">
+        <f>IF(ABS(B6)&lt;=C6,1,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" s="28">
-        <f>IF(SUM(D2:D5)=4,1,0)</f>
+      <c r="A7" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="27">
+        <f>Charts!$G$11-Charts!$B$5-SUM(Charts!$B$6:Charts!$B$10)</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="28">
+        <v>0.001</v>
+      </c>
+      <c r="D7" s="29">
+        <f>IF(ABS(B7)&lt;=C7,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D9" s="30">
+        <f>IF(SUM(D2:D7)=COUNT(D2:D7),1,0)</f>
         <v>1</v>
       </c>
     </row>

--- a/data/valuation/jordan_valuation.xlsx
+++ b/data/valuation/jordan_valuation.xlsx
@@ -280,6 +280,91 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="G42" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: presentation convention (marker bar width as a share of the value)</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: model convention (check tolerance; must exceed float and iteration noise)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: model convention (check tolerance; must exceed float and iteration noise)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: model convention (check tolerance; must exceed float and iteration noise)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: model convention (check tolerance; must exceed float and iteration noise)</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="142">
   <si>
@@ -649,7 +734,7 @@
     <t>Value = PV(FCF) + PV(TV)</t>
   </si>
   <si>
-    <t>Discount timing ends at 4.63 years</t>
+    <t>Discount timing: final period ends at stub + (periods - 1) years</t>
   </si>
   <si>
     <t>Jordan DCF value, active scenario ($m): bars reconcile</t>
@@ -3243,6 +3328,7 @@
     <brk id="34" max="16383" man="1"/>
   </rowBreaks>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3338,7 +3424,7 @@
         <v>122</v>
       </c>
       <c r="B6" s="27">
-        <f>Model!$G$7-(Inputs!$C$19+4)</f>
+        <f>Model!$G$7-(Inputs!$C$19+MAX(Model!$C$5:$G$5)-1)</f>
         <v>0</v>
       </c>
       <c r="C6" s="28">
@@ -3376,5 +3462,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/valuation/jordan_valuation.xlsx
+++ b/data/valuation/jordan_valuation.xlsx
@@ -3440,7 +3440,7 @@
         <v>123</v>
       </c>
       <c r="B7" s="27">
-        <f>Charts!$G$11-Charts!$B$5-SUM(Charts!$B$6:Charts!$B$10)</f>
+        <f>Charts!$G$11-Charts!$B$5-SUM(Charts!$B$6:$B$10)</f>
         <v>0</v>
       </c>
       <c r="C7" s="28">

--- a/data/valuation/jordan_valuation.xlsx
+++ b/data/valuation/jordan_valuation.xlsx
@@ -366,7 +366,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="143">
   <si>
     <t>Inputs</t>
   </si>
@@ -567,6 +567,9 @@
   </si>
   <si>
     <t>Discount factor</t>
+  </si>
+  <si>
+    <t>factor</t>
   </si>
   <si>
     <t>PV of free cash flow</t>
@@ -798,16 +801,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="@"/>
     <numFmt numFmtId="165" formatCode="#,##0_);(#,##0);&quot;-&quot;_)"/>
     <numFmt numFmtId="166" formatCode="$#,##0.00_);($#,##0.00);&quot;-&quot;_)"/>
     <numFmt numFmtId="167" formatCode="0.0%_);(0.0%);&quot;-&quot;_)"/>
     <numFmt numFmtId="168" formatCode="0.0&quot;x&quot;"/>
     <numFmt numFmtId="169" formatCode="0.00"/>
-    <numFmt numFmtId="170" formatCode="0.0%"/>
-    <numFmt numFmtId="171" formatCode="#,##0.000000"/>
-    <numFmt numFmtId="172" formatCode="0.000000"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="171" formatCode="0.0%"/>
+    <numFmt numFmtId="172" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="173" formatCode="0.000000"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -927,13 +931,13 @@
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
@@ -1881,17 +1885,17 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B4" s="1" t="str">
         <f>IF(MasterCheck=1,"OK: all checks pass","ERROR: see Checks sheet")</f>
@@ -1900,44 +1904,44 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1945,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1953,23 +1957,23 @@
         <v>41</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2725,7 +2729,7 @@
         <v>66</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C21" s="22">
         <f>1/(1+Inputs!$C$17)^C8</f>
@@ -2750,7 +2754,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>16</v>
@@ -2802,7 +2806,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2821,12 +2825,12 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>16</v>
@@ -2838,7 +2842,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>16</v>
@@ -2850,7 +2854,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>16</v>
@@ -2862,12 +2866,12 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>16</v>
@@ -2879,7 +2883,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>16</v>
@@ -2891,7 +2895,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>21</v>
@@ -2903,7 +2907,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>27</v>
@@ -2915,7 +2919,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>27</v>
@@ -2927,12 +2931,12 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>16</v>
@@ -2944,7 +2948,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>21</v>
@@ -2956,7 +2960,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>27</v>
@@ -2990,40 +2994,40 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B5" s="24">
         <f>Model!$C$22</f>
@@ -3043,7 +3047,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B6" s="24">
         <f>Model!$D$22</f>
@@ -3069,7 +3073,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B7" s="24">
         <f>Model!$E$22</f>
@@ -3095,7 +3099,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B8" s="24">
         <f>Model!$F$22</f>
@@ -3121,7 +3125,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B9" s="24">
         <f>Model!$G$22</f>
@@ -3147,7 +3151,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B10" s="24">
         <f>Valuation!$C$7</f>
@@ -3173,7 +3177,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C11" s="10">
         <f>C10</f>
@@ -3189,34 +3193,34 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B38" s="12">
         <v>2.32</v>
@@ -3229,12 +3233,12 @@
         <v>3.64</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B39" s="12">
         <v>2.14</v>
@@ -3247,12 +3251,12 @@
         <v>3.64</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B40" s="12">
         <v>1.82</v>
@@ -3265,12 +3269,12 @@
         <v>2.75</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B41" s="12">
         <v>5.68</v>
@@ -3283,12 +3287,12 @@
         <v>0.0199999999999996</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B42" s="23">
         <f>F42-ABS(F42)*G42</f>
@@ -3303,7 +3307,7 @@
         <v>0.0379251875838893</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F42" s="25">
         <f>Valuation!$C$11</f>
@@ -3315,7 +3319,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -3343,21 +3347,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B2" s="27">
         <f>Model!$G$16-Inputs!$C$21</f>
@@ -3373,14 +3377,14 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B3" s="29">
         <f>IF(Inputs!$C$22&lt;Inputs!$C$17,1,0)</f>
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D3" s="29">
         <f>B3</f>
@@ -3389,14 +3393,14 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B4" s="29">
         <f>IF(MIN(Model!$C$14:$G$14)&gt;=0,1,0)</f>
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D4" s="29">
         <f>B4</f>
@@ -3405,7 +3409,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B5" s="27">
         <f>Valuation!$C$10-SUM(Model!$C$22:$G$22)-Valuation!$C$7</f>
@@ -3421,7 +3425,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B6" s="27">
         <f>Model!$G$7-(Inputs!$C$19+MAX(Model!$C$5:$G$5)-1)</f>
@@ -3437,7 +3441,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B7" s="27">
         <f>Charts!$G$11-Charts!$B$5-SUM(Charts!$B$6:$B$10)</f>
@@ -3453,7 +3457,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D9" s="30">
         <f>IF(SUM(D2:D7)=COUNT(D2:D7),1,0)</f>
